--- a/outputs/daily/hr_rankings_2026-09-20.xlsx
+++ b/outputs/daily/hr_rankings_2026-09-20.xlsx
@@ -12423,27 +12423,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>682674</t>
+          <t>666176</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Victor Bericoto</t>
+          <t>Jo Adell</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-20T20:10:00Z</t>
+          <t>2026-09-20T17:40:00Z</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -12453,14 +12453,26 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Jack Perkins</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>678022</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L45" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -12478,22 +12490,22 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>53.5</v>
+        <v>52.7</v>
       </c>
       <c r="Q45" t="n">
-        <v>41.2</v>
+        <v>41</v>
       </c>
       <c r="R45" t="n">
         <v>27.6</v>
       </c>
       <c r="S45" t="n">
-        <v>92.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T45" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U45" t="n">
-        <v>37.8</v>
+        <v>65.2</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
@@ -12507,7 +12519,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -12532,7 +12544,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>H:2026 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr"/>
@@ -12549,110 +12561,134 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/16, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL45" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.2% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>90.65</t>
         </is>
       </c>
       <c r="AQ45" t="inlineStr">
         <is>
-          <t>100.3441</t>
+          <t>102.9391</t>
         </is>
       </c>
       <c r="AR45" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.4741</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.2155</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>0.3384</t>
         </is>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>77.39</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>72.04</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>39.61</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>0.173</t>
-        </is>
-      </c>
-      <c r="BA45" t="inlineStr"/>
-      <c r="BB45" t="inlineStr"/>
-      <c r="BC45" t="inlineStr"/>
-      <c r="BD45" t="inlineStr"/>
-      <c r="BE45" t="inlineStr"/>
-      <c r="BF45" t="inlineStr"/>
+          <t>0.1881</t>
+        </is>
+      </c>
+      <c r="BA45" t="inlineStr">
+        <is>
+          <t>9.18</t>
+        </is>
+      </c>
+      <c r="BB45" t="inlineStr">
+        <is>
+          <t>36.86</t>
+        </is>
+      </c>
+      <c r="BC45" t="inlineStr">
+        <is>
+          <t>87.94</t>
+        </is>
+      </c>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>0.3769</t>
+        </is>
+      </c>
+      <c r="BE45" t="inlineStr">
+        <is>
+          <t>0.1503</t>
+        </is>
+      </c>
+      <c r="BF45" t="inlineStr">
+        <is>
+          <t>33.12</t>
+        </is>
+      </c>
       <c r="BG45" t="inlineStr"/>
       <c r="BH45" t="inlineStr"/>
       <c r="BI45" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ45" t="inlineStr"/>
@@ -12663,27 +12699,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>666176</t>
+          <t>682674</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jo Adell</t>
+          <t>Victor Bericoto</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-20T17:40:00Z</t>
+          <t>2026-09-20T20:10:00Z</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -12693,24 +12729,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Jack Perkins</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>678022</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
       <c r="L46" t="n">
         <v>51.8</v>
       </c>
@@ -12730,22 +12754,22 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>52.7</v>
+        <v>53.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>41</v>
+        <v>41.2</v>
       </c>
       <c r="R46" t="n">
         <v>27.6</v>
       </c>
       <c r="S46" t="n">
-        <v>90.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T46" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U46" t="n">
-        <v>65.2</v>
+        <v>35.6</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
@@ -12759,7 +12783,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -12784,7 +12808,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr"/>
@@ -12801,134 +12825,110 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/17, 1 HR</t>
         </is>
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.2% barrel, 15.2 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>11.49</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>90.65</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AQ46" t="inlineStr">
         <is>
-          <t>102.9391</t>
+          <t>100.3441</t>
         </is>
       </c>
       <c r="AR46" t="inlineStr">
         <is>
-          <t>0.4741</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr">
         <is>
-          <t>0.2155</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr">
         <is>
-          <t>0.3384</t>
+          <t>0.282</t>
         </is>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>77.39</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>72.04</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>39.61</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>0.1881</t>
-        </is>
-      </c>
-      <c r="BA46" t="inlineStr">
-        <is>
-          <t>9.18</t>
-        </is>
-      </c>
-      <c r="BB46" t="inlineStr">
-        <is>
-          <t>36.86</t>
-        </is>
-      </c>
-      <c r="BC46" t="inlineStr">
-        <is>
-          <t>87.94</t>
-        </is>
-      </c>
-      <c r="BD46" t="inlineStr">
-        <is>
-          <t>0.3769</t>
-        </is>
-      </c>
-      <c r="BE46" t="inlineStr">
-        <is>
-          <t>0.1503</t>
-        </is>
-      </c>
-      <c r="BF46" t="inlineStr">
-        <is>
-          <t>33.12</t>
-        </is>
-      </c>
+          <t>0.173</t>
+        </is>
+      </c>
+      <c r="BA46" t="inlineStr"/>
+      <c r="BB46" t="inlineStr"/>
+      <c r="BC46" t="inlineStr"/>
+      <c r="BD46" t="inlineStr"/>
+      <c r="BE46" t="inlineStr"/>
+      <c r="BF46" t="inlineStr"/>
       <c r="BG46" t="inlineStr"/>
       <c r="BH46" t="inlineStr"/>
       <c r="BI46" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ46" t="inlineStr"/>
@@ -31863,27 +31863,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>667472</t>
+          <t>668904</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Dane Myers</t>
+          <t>Royce Lewis</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-09-20T17:40:00Z</t>
+          <t>2026-09-20T20:07:00Z</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -31893,14 +31893,26 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Ryan Johnson</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>696270</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L117" t="n">
-        <v>43.5</v>
+        <v>43.7</v>
       </c>
       <c r="M117" t="inlineStr">
         <is>
@@ -31914,26 +31926,26 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P117" t="n">
-        <v>26</v>
+        <v>40.4</v>
       </c>
       <c r="Q117" t="n">
-        <v>41.2</v>
+        <v>46.1</v>
       </c>
       <c r="R117" t="n">
-        <v>39.3</v>
+        <v>28.2</v>
       </c>
       <c r="S117" t="n">
-        <v>88.7</v>
+        <v>71.7</v>
       </c>
       <c r="T117" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U117" t="n">
-        <v>25.3</v>
+        <v>10.8</v>
       </c>
       <c r="V117" t="inlineStr">
         <is>
@@ -31947,7 +31959,7 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y117" t="inlineStr">
@@ -31972,7 +31984,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD117" t="inlineStr"/>
@@ -31989,110 +32001,134 @@
       </c>
       <c r="AH117" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 5/26, 0 HR</t>
         </is>
       </c>
       <c r="AL117" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.5% barrel, 13.8 HR allowed</t>
         </is>
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN117" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>38.43</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>89.86</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AQ117" t="inlineStr">
         <is>
-          <t>99.1984</t>
+          <t>100.593</t>
         </is>
       </c>
       <c r="AR117" t="inlineStr">
         <is>
-          <t>0.3677</t>
+          <t>0.3979</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr">
         <is>
-          <t>0.1267</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr">
         <is>
-          <t>0.3099</t>
+          <t>0.304</t>
         </is>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>71.04</t>
+          <t>74.65</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>49.82</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>28.49</t>
+          <t>46.51</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>30.78</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>0.1078</t>
-        </is>
-      </c>
-      <c r="BA117" t="inlineStr"/>
-      <c r="BB117" t="inlineStr"/>
-      <c r="BC117" t="inlineStr"/>
-      <c r="BD117" t="inlineStr"/>
-      <c r="BE117" t="inlineStr"/>
-      <c r="BF117" t="inlineStr"/>
+          <t>0.1531</t>
+        </is>
+      </c>
+      <c r="BA117" t="inlineStr">
+        <is>
+          <t>9.48</t>
+        </is>
+      </c>
+      <c r="BB117" t="inlineStr">
+        <is>
+          <t>36.42</t>
+        </is>
+      </c>
+      <c r="BC117" t="inlineStr">
+        <is>
+          <t>87.68</t>
+        </is>
+      </c>
+      <c r="BD117" t="inlineStr">
+        <is>
+          <t>0.4332</t>
+        </is>
+      </c>
+      <c r="BE117" t="inlineStr">
+        <is>
+          <t>0.1833</t>
+        </is>
+      </c>
+      <c r="BF117" t="inlineStr">
+        <is>
+          <t>34.09</t>
+        </is>
+      </c>
       <c r="BG117" t="inlineStr"/>
       <c r="BH117" t="inlineStr"/>
       <c r="BI117" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ117" t="inlineStr"/>
@@ -32103,22 +32139,22 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>683748</t>
+          <t>667472</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Dane Myers</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -32133,24 +32169,12 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>Patrick Sandoval</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>663776</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
       <c r="L118" t="n">
         <v>43.5</v>
       </c>
@@ -32166,26 +32190,26 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P118" t="n">
-        <v>44.4</v>
+        <v>26</v>
       </c>
       <c r="Q118" t="n">
-        <v>34.3</v>
+        <v>41.2</v>
       </c>
       <c r="R118" t="n">
-        <v>27.6</v>
+        <v>39.3</v>
       </c>
       <c r="S118" t="n">
-        <v>71.7</v>
+        <v>88.7</v>
       </c>
       <c r="T118" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U118" t="n">
-        <v>39.5</v>
+        <v>25.3</v>
       </c>
       <c r="V118" t="inlineStr">
         <is>
@@ -32199,7 +32223,7 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y118" t="inlineStr">
@@ -32224,7 +32248,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD118" t="inlineStr"/>
@@ -32241,12 +32265,12 @@
       </c>
       <c r="AH118" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ118" t="inlineStr">
@@ -32256,12 +32280,12 @@
       </c>
       <c r="AK118" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/23, 1 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL118" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 6.0 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM118" t="inlineStr">
@@ -32271,104 +32295,80 @@
       </c>
       <c r="AN118" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>38.43</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>89.77</t>
+          <t>89.86</t>
         </is>
       </c>
       <c r="AQ118" t="inlineStr">
         <is>
-          <t>100.1512</t>
+          <t>99.1984</t>
         </is>
       </c>
       <c r="AR118" t="inlineStr">
         <is>
-          <t>0.4395</t>
+          <t>0.3677</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr">
         <is>
-          <t>0.1942</t>
+          <t>0.1267</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr">
         <is>
-          <t>0.334</t>
+          <t>0.3099</t>
         </is>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>73.72</t>
+          <t>71.04</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>32.74</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>40.52</t>
+          <t>28.49</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>34.54</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>0.2176</t>
-        </is>
-      </c>
-      <c r="BA118" t="inlineStr">
-        <is>
-          <t>6.9</t>
-        </is>
-      </c>
-      <c r="BB118" t="inlineStr">
-        <is>
-          <t>36.0</t>
-        </is>
-      </c>
-      <c r="BC118" t="inlineStr">
-        <is>
-          <t>87.8</t>
-        </is>
-      </c>
-      <c r="BD118" t="inlineStr">
-        <is>
-          <t>0.442</t>
-        </is>
-      </c>
-      <c r="BE118" t="inlineStr">
-        <is>
-          <t>0.163</t>
-        </is>
-      </c>
-      <c r="BF118" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
+          <t>0.1078</t>
+        </is>
+      </c>
+      <c r="BA118" t="inlineStr"/>
+      <c r="BB118" t="inlineStr"/>
+      <c r="BC118" t="inlineStr"/>
+      <c r="BD118" t="inlineStr"/>
+      <c r="BE118" t="inlineStr"/>
+      <c r="BF118" t="inlineStr"/>
       <c r="BG118" t="inlineStr"/>
       <c r="BH118" t="inlineStr"/>
       <c r="BI118" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ118" t="inlineStr"/>
@@ -32379,27 +32379,27 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>814430</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Brett Callahan</t>
+          <t>Victor Mesa</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-09-20T18:10:00Z</t>
+          <t>2026-09-20T17:40:00Z</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -32409,22 +32409,22 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Davis Martin</t>
+          <t>Patrick Sandoval</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>663436</t>
+          <t>663776</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L119" t="n">
@@ -32442,26 +32442,26 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P119" t="n">
-        <v>43.3</v>
+        <v>44.4</v>
       </c>
       <c r="Q119" t="n">
-        <v>44.8</v>
+        <v>34.3</v>
       </c>
       <c r="R119" t="n">
         <v>27.6</v>
       </c>
       <c r="S119" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T119" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U119" t="n">
-        <v>7</v>
+        <v>39.5</v>
       </c>
       <c r="V119" t="inlineStr">
         <is>
@@ -32475,7 +32475,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y119" t="inlineStr">
@@ -32500,7 +32500,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD119" t="inlineStr"/>
@@ -32517,134 +32517,134 @@
       </c>
       <c r="AH119" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/12, 0 HR</t>
+          <t>Last 7 games: 6/23, 1 HR</t>
         </is>
       </c>
       <c r="AL119" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.4% barrel, 15.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.9% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN119" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.77</t>
         </is>
       </c>
       <c r="AQ119" t="inlineStr">
         <is>
-          <t>100.7322</t>
+          <t>100.1512</t>
         </is>
       </c>
       <c r="AR119" t="inlineStr">
         <is>
-          <t>0.377</t>
+          <t>0.4395</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr">
         <is>
+          <t>0.1942</t>
+        </is>
+      </c>
+      <c r="AT119" t="inlineStr">
+        <is>
+          <t>0.334</t>
+        </is>
+      </c>
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>73.72</t>
+        </is>
+      </c>
+      <c r="AV119" t="inlineStr">
+        <is>
+          <t>32.74</t>
+        </is>
+      </c>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>40.52</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>34.54</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
+      </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>0.2176</t>
+        </is>
+      </c>
+      <c r="BA119" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="BB119" t="inlineStr">
+        <is>
+          <t>36.0</t>
+        </is>
+      </c>
+      <c r="BC119" t="inlineStr">
+        <is>
+          <t>87.8</t>
+        </is>
+      </c>
+      <c r="BD119" t="inlineStr">
+        <is>
+          <t>0.442</t>
+        </is>
+      </c>
+      <c r="BE119" t="inlineStr">
+        <is>
           <t>0.163</t>
         </is>
       </c>
-      <c r="AT119" t="inlineStr">
-        <is>
-          <t>0.297</t>
-        </is>
-      </c>
-      <c r="AU119" t="inlineStr">
-        <is>
-          <t>74.6</t>
-        </is>
-      </c>
-      <c r="AV119" t="inlineStr">
-        <is>
-          <t>46.7</t>
-        </is>
-      </c>
-      <c r="AW119" t="inlineStr">
-        <is>
-          <t>37.1</t>
-        </is>
-      </c>
-      <c r="AX119" t="inlineStr">
-        <is>
-          <t>37.1</t>
-        </is>
-      </c>
-      <c r="AY119" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AZ119" t="inlineStr">
-        <is>
-          <t>0.143</t>
-        </is>
-      </c>
-      <c r="BA119" t="inlineStr">
-        <is>
-          <t>7.42</t>
-        </is>
-      </c>
-      <c r="BB119" t="inlineStr">
-        <is>
-          <t>44.67</t>
-        </is>
-      </c>
-      <c r="BC119" t="inlineStr">
-        <is>
-          <t>90.42</t>
-        </is>
-      </c>
-      <c r="BD119" t="inlineStr">
-        <is>
-          <t>0.4293</t>
-        </is>
-      </c>
-      <c r="BE119" t="inlineStr">
-        <is>
-          <t>0.1573</t>
-        </is>
-      </c>
       <c r="BF119" t="inlineStr">
         <is>
-          <t>23.97</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="BG119" t="inlineStr"/>
       <c r="BH119" t="inlineStr"/>
       <c r="BI119" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ119" t="inlineStr"/>
@@ -32655,27 +32655,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>668904</t>
+          <t>814430</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Royce Lewis</t>
+          <t>Brett Callahan</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-09-20T20:07:00Z</t>
+          <t>2026-09-20T18:10:00Z</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -32685,17 +32685,17 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Ryan Johnson</t>
+          <t>Davis Martin</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>696270</t>
+          <t>663436</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -32718,26 +32718,26 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P120" t="n">
-        <v>40.4</v>
+        <v>43.3</v>
       </c>
       <c r="Q120" t="n">
-        <v>46.1</v>
+        <v>44.8</v>
       </c>
       <c r="R120" t="n">
-        <v>28.2</v>
+        <v>27.6</v>
       </c>
       <c r="S120" t="n">
-        <v>71.7</v>
+        <v>47.9</v>
       </c>
       <c r="T120" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U120" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V120" t="inlineStr">
         <is>
@@ -32751,7 +32751,7 @@
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y120" t="inlineStr">
@@ -32776,7 +32776,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD120" t="inlineStr"/>
@@ -32793,12 +32793,12 @@
       </c>
       <c r="AH120" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AJ120" t="inlineStr">
@@ -32808,119 +32808,119 @@
       </c>
       <c r="AK120" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/25, 0 HR</t>
+          <t>Last 7 games: 2/12, 0 HR</t>
         </is>
       </c>
       <c r="AL120" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.5% barrel, 13.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.4% barrel, 15.8 HR allowed</t>
         </is>
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN120" t="inlineStr">
         <is>
-          <t>10.31</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AQ120" t="inlineStr">
         <is>
-          <t>100.593</t>
+          <t>100.7322</t>
         </is>
       </c>
       <c r="AR120" t="inlineStr">
         <is>
-          <t>0.3979</t>
+          <t>0.377</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.163</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>0.297</t>
         </is>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>74.65</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>49.82</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>46.51</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>30.78</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>0.1531</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>9.48</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>36.42</t>
+          <t>44.67</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>87.68</t>
+          <t>90.42</t>
         </is>
       </c>
       <c r="BD120" t="inlineStr">
         <is>
-          <t>0.4332</t>
+          <t>0.4293</t>
         </is>
       </c>
       <c r="BE120" t="inlineStr">
         <is>
-          <t>0.1833</t>
+          <t>0.1573</t>
         </is>
       </c>
       <c r="BF120" t="inlineStr">
         <is>
-          <t>34.09</t>
+          <t>23.97</t>
         </is>
       </c>
       <c r="BG120" t="inlineStr"/>
       <c r="BH120" t="inlineStr"/>
       <c r="BI120" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ120" t="inlineStr"/>
@@ -36074,7 +36074,7 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ132" t="inlineStr">
@@ -39483,24 +39483,24 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>685133</t>
+          <t>605170</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Wade Meckler</t>
+          <t>Victor Caratini</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
           <t>LAA</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
       <c r="F145" t="inlineStr">
         <is>
           <t>2026-09-20T20:07:00Z</t>
@@ -39513,17 +39513,17 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Dean Kremer</t>
+          <t>Ryan Johnson</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>665152</t>
+          <t>696270</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -39546,26 +39546,26 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P145" t="n">
-        <v>11.5</v>
+        <v>29.6</v>
       </c>
       <c r="Q145" t="n">
-        <v>47.7</v>
+        <v>44.6</v>
       </c>
       <c r="R145" t="n">
         <v>28.2</v>
       </c>
       <c r="S145" t="n">
-        <v>92.09999999999999</v>
+        <v>59.8</v>
       </c>
       <c r="T145" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U145" t="n">
-        <v>25.8</v>
+        <v>19.5</v>
       </c>
       <c r="V145" t="inlineStr">
         <is>
@@ -39579,7 +39579,7 @@
       </c>
       <c r="X145" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y145" t="inlineStr">
@@ -39604,7 +39604,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD145" t="inlineStr"/>
@@ -39621,12 +39621,12 @@
       </c>
       <c r="AH145" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ145" t="inlineStr">
@@ -39636,12 +39636,12 @@
       </c>
       <c r="AK145" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL145" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.3% barrel, 18.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.5% barrel, 13.8 HR allowed</t>
         </is>
       </c>
       <c r="AM145" t="inlineStr">
@@ -39651,97 +39651,97 @@
       </c>
       <c r="AN145" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.19</t>
         </is>
       </c>
       <c r="AQ145" t="inlineStr">
         <is>
-          <t>96.6684</t>
+          <t>98.9527</t>
         </is>
       </c>
       <c r="AR145" t="inlineStr">
         <is>
-          <t>0.351</t>
+          <t>0.3844</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>0.1476</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>71.39</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>16.29</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>37.71</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>23.06</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>0.1107</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>9.48</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>36.42</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>87.96</t>
+          <t>87.68</t>
         </is>
       </c>
       <c r="BD145" t="inlineStr">
         <is>
-          <t>0.4419</t>
+          <t>0.4332</t>
         </is>
       </c>
       <c r="BE145" t="inlineStr">
         <is>
-          <t>0.1987</t>
+          <t>0.1833</t>
         </is>
       </c>
       <c r="BF145" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>34.09</t>
         </is>
       </c>
       <c r="BG145" t="inlineStr"/>
@@ -39759,27 +39759,27 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>682663</t>
+          <t>685133</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Agustin Ramirez</t>
+          <t>Wade Meckler</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-09-20T20:10:00Z</t>
+          <t>2026-09-20T20:07:00Z</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -39789,17 +39789,17 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Walker Buehler</t>
+          <t>Dean Kremer</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>621111</t>
+          <t>665152</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -39822,26 +39822,26 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P146" t="n">
-        <v>31</v>
+        <v>11.5</v>
       </c>
       <c r="Q146" t="n">
-        <v>43</v>
+        <v>47.7</v>
       </c>
       <c r="R146" t="n">
-        <v>22.6</v>
+        <v>28.2</v>
       </c>
       <c r="S146" t="n">
-        <v>59.8</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T146" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U146" t="n">
-        <v>78.7</v>
+        <v>25.8</v>
       </c>
       <c r="V146" t="inlineStr">
         <is>
@@ -39855,7 +39855,7 @@
       </c>
       <c r="X146" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y146" t="inlineStr">
@@ -39880,7 +39880,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD146" t="inlineStr"/>
@@ -39897,134 +39897,134 @@
       </c>
       <c r="AH146" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 7/24, 0 HR</t>
         </is>
       </c>
       <c r="AL146" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.6% barrel, 20.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.3% barrel, 18.5 HR allowed</t>
         </is>
       </c>
       <c r="AM146" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN146" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>42.38</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>90.03</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ146" t="inlineStr">
         <is>
-          <t>102.6626</t>
+          <t>96.6684</t>
         </is>
       </c>
       <c r="AR146" t="inlineStr">
         <is>
-          <t>0.3604</t>
+          <t>0.351</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr">
         <is>
-          <t>0.1266</t>
+          <t>0.094</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr">
         <is>
-          <t>0.2998</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>75.62</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>56.67</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>18.63</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>0.1463</t>
+          <t>0.086</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>35.66</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>88.88</t>
+          <t>87.96</t>
         </is>
       </c>
       <c r="BD146" t="inlineStr">
         <is>
-          <t>0.4171</t>
+          <t>0.4419</t>
         </is>
       </c>
       <c r="BE146" t="inlineStr">
         <is>
-          <t>0.1645</t>
+          <t>0.1987</t>
         </is>
       </c>
       <c r="BF146" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="BG146" t="inlineStr"/>
       <c r="BH146" t="inlineStr"/>
       <c r="BI146" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ146" t="inlineStr"/>
@@ -40311,27 +40311,27 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>682877</t>
+          <t>682663</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Juan Brito</t>
+          <t>Agustin Ramirez</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-09-20T17:40:00Z</t>
+          <t>2026-09-20T20:10:00Z</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -40341,14 +40341,26 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Walker Buehler</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>621111</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L148" t="n">
-        <v>40.5</v>
+        <v>40.6</v>
       </c>
       <c r="M148" t="inlineStr">
         <is>
@@ -40362,26 +40374,26 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P148" t="n">
-        <v>16.6</v>
+        <v>31</v>
       </c>
       <c r="Q148" t="n">
-        <v>40.2</v>
+        <v>43</v>
       </c>
       <c r="R148" t="n">
-        <v>39.3</v>
+        <v>22.6</v>
       </c>
       <c r="S148" t="n">
-        <v>71.7</v>
+        <v>59.8</v>
       </c>
       <c r="T148" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U148" t="n">
-        <v>54.3</v>
+        <v>75.8</v>
       </c>
       <c r="V148" t="inlineStr">
         <is>
@@ -40395,7 +40407,7 @@
       </c>
       <c r="X148" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y148" t="inlineStr">
@@ -40420,7 +40432,7 @@
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>H:2026 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD148" t="inlineStr"/>
@@ -40437,27 +40449,27 @@
       </c>
       <c r="AH148" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
         <is>
-          <t>Contact streak: 9/25 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL148" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.6% barrel, 20.6 HR allowed</t>
         </is>
       </c>
       <c r="AM148" t="inlineStr">
@@ -40467,80 +40479,104 @@
       </c>
       <c r="AN148" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>42.38</t>
         </is>
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>90.03</t>
         </is>
       </c>
       <c r="AQ148" t="inlineStr">
         <is>
-          <t>96.9148</t>
+          <t>102.6626</t>
         </is>
       </c>
       <c r="AR148" t="inlineStr">
         <is>
-          <t>0.359</t>
+          <t>0.3604</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>0.1266</t>
         </is>
       </c>
       <c r="AT148" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>0.2998</t>
         </is>
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>75.62</t>
         </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>56.67</t>
         </is>
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>18.63</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>0.138</t>
-        </is>
-      </c>
-      <c r="BA148" t="inlineStr"/>
-      <c r="BB148" t="inlineStr"/>
-      <c r="BC148" t="inlineStr"/>
-      <c r="BD148" t="inlineStr"/>
-      <c r="BE148" t="inlineStr"/>
-      <c r="BF148" t="inlineStr"/>
+          <t>0.1463</t>
+        </is>
+      </c>
+      <c r="BA148" t="inlineStr">
+        <is>
+          <t>8.59</t>
+        </is>
+      </c>
+      <c r="BB148" t="inlineStr">
+        <is>
+          <t>38.15</t>
+        </is>
+      </c>
+      <c r="BC148" t="inlineStr">
+        <is>
+          <t>88.88</t>
+        </is>
+      </c>
+      <c r="BD148" t="inlineStr">
+        <is>
+          <t>0.4171</t>
+        </is>
+      </c>
+      <c r="BE148" t="inlineStr">
+        <is>
+          <t>0.1645</t>
+        </is>
+      </c>
+      <c r="BF148" t="inlineStr">
+        <is>
+          <t>23.44</t>
+        </is>
+      </c>
       <c r="BG148" t="inlineStr"/>
       <c r="BH148" t="inlineStr"/>
       <c r="BI148" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ148" t="inlineStr"/>
@@ -40551,22 +40587,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>682877</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Juan Brito</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -40581,24 +40617,12 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>Jack Perkins</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>678022</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
       <c r="L149" t="n">
         <v>40.5</v>
       </c>
@@ -40614,26 +40638,26 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P149" t="n">
-        <v>21.6</v>
+        <v>16.6</v>
       </c>
       <c r="Q149" t="n">
-        <v>41</v>
+        <v>40.2</v>
       </c>
       <c r="R149" t="n">
-        <v>27.6</v>
+        <v>39.3</v>
       </c>
       <c r="S149" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T149" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U149" t="n">
-        <v>75.90000000000001</v>
+        <v>54.3</v>
       </c>
       <c r="V149" t="inlineStr">
         <is>
@@ -40647,7 +40671,7 @@
       </c>
       <c r="X149" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y149" t="inlineStr">
@@ -40672,7 +40696,7 @@
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026 P:</t>
         </is>
       </c>
       <c r="AD149" t="inlineStr"/>
@@ -40689,67 +40713,67 @@
       </c>
       <c r="AH149" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
         <is>
-          <t>Hot streak: 4 HR in last 7 games</t>
+          <t>Contact streak: 9/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL149" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.2% barrel, 15.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN149" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AO149" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AQ149" t="inlineStr">
         <is>
-          <t>98.4634</t>
+          <t>96.9148</t>
         </is>
       </c>
       <c r="AR149" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>0.359</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.128</t>
         </is>
       </c>
       <c r="AT149" t="inlineStr">
         <is>
-          <t>0.305</t>
+          <t>0.285</t>
         </is>
       </c>
       <c r="AU149" t="inlineStr">
@@ -40759,64 +40783,40 @@
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>0.164</t>
-        </is>
-      </c>
-      <c r="BA149" t="inlineStr">
-        <is>
-          <t>9.18</t>
-        </is>
-      </c>
-      <c r="BB149" t="inlineStr">
-        <is>
-          <t>36.86</t>
-        </is>
-      </c>
-      <c r="BC149" t="inlineStr">
-        <is>
-          <t>87.94</t>
-        </is>
-      </c>
-      <c r="BD149" t="inlineStr">
-        <is>
-          <t>0.3769</t>
-        </is>
-      </c>
-      <c r="BE149" t="inlineStr">
-        <is>
-          <t>0.1503</t>
-        </is>
-      </c>
-      <c r="BF149" t="inlineStr">
-        <is>
-          <t>33.12</t>
-        </is>
-      </c>
+          <t>0.138</t>
+        </is>
+      </c>
+      <c r="BA149" t="inlineStr"/>
+      <c r="BB149" t="inlineStr"/>
+      <c r="BC149" t="inlineStr"/>
+      <c r="BD149" t="inlineStr"/>
+      <c r="BE149" t="inlineStr"/>
+      <c r="BF149" t="inlineStr"/>
       <c r="BG149" t="inlineStr"/>
       <c r="BH149" t="inlineStr"/>
       <c r="BI149" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ149" t="inlineStr"/>
@@ -40827,22 +40827,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>596115</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Trevor Story</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -40857,17 +40857,17 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Griffin Jax</t>
+          <t>Jack Perkins</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>643377</t>
+          <t>678022</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -40890,26 +40890,26 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P150" t="n">
-        <v>26.5</v>
+        <v>21.6</v>
       </c>
       <c r="Q150" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="R150" t="n">
         <v>27.6</v>
       </c>
       <c r="S150" t="n">
-        <v>71.7</v>
+        <v>59.8</v>
       </c>
       <c r="T150" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U150" t="n">
-        <v>54.3</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="V150" t="inlineStr">
         <is>
@@ -40923,7 +40923,7 @@
       </c>
       <c r="X150" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y150" t="inlineStr">
@@ -40948,7 +40948,7 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD150" t="inlineStr"/>
@@ -40965,134 +40965,134 @@
       </c>
       <c r="AH150" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
         <is>
-          <t>Contact streak: 9/25 over last 7 games</t>
+          <t>Hot streak: 4 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL150" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.3% barrel, 12.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.2% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM150" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN150" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO150" t="inlineStr">
         <is>
-          <t>40.56</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>88.53</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="AQ150" t="inlineStr">
         <is>
-          <t>99.7938</t>
+          <t>98.4634</t>
         </is>
       </c>
       <c r="AR150" t="inlineStr">
         <is>
-          <t>0.3559</t>
+          <t>0.352</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr">
         <is>
-          <t>0.1275</t>
+          <t>0.124</t>
         </is>
       </c>
       <c r="AT150" t="inlineStr">
         <is>
-          <t>0.2711</t>
+          <t>0.305</t>
         </is>
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>71.03</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>13.75</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>41.74</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>24.81</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>0.1294</t>
+          <t>0.164</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>9.18</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>41.51</t>
+          <t>36.86</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>88.99</t>
+          <t>87.94</t>
         </is>
       </c>
       <c r="BD150" t="inlineStr">
         <is>
-          <t>0.3993</t>
+          <t>0.3769</t>
         </is>
       </c>
       <c r="BE150" t="inlineStr">
         <is>
-          <t>0.1534</t>
+          <t>0.1503</t>
         </is>
       </c>
       <c r="BF150" t="inlineStr">
         <is>
-          <t>23.37</t>
+          <t>33.12</t>
         </is>
       </c>
       <c r="BG150" t="inlineStr"/>
       <c r="BH150" t="inlineStr"/>
       <c r="BI150" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ150" t="inlineStr"/>
@@ -41103,27 +41103,27 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>662139</t>
+          <t>596115</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Daulton Varsho</t>
+          <t>Trevor Story</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-09-20T18:10:00Z</t>
+          <t>2026-09-20T17:40:00Z</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -41138,17 +41138,17 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Martín Pérez</t>
+          <t>Griffin Jax</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>527048</t>
+          <t>643377</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L151" t="n">
@@ -41170,10 +41170,10 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>35.9</v>
+        <v>26.5</v>
       </c>
       <c r="Q151" t="n">
-        <v>37.7</v>
+        <v>43</v>
       </c>
       <c r="R151" t="n">
         <v>27.6</v>
@@ -41185,7 +41185,7 @@
         <v>50</v>
       </c>
       <c r="U151" t="n">
-        <v>18.3</v>
+        <v>54.3</v>
       </c>
       <c r="V151" t="inlineStr">
         <is>
@@ -41241,12 +41241,12 @@
       </c>
       <c r="AH151" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ151" t="inlineStr">
@@ -41256,12 +41256,12 @@
       </c>
       <c r="AK151" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/24, 1 HR</t>
+          <t>Contact streak: 9/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL151" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.9% barrel, 10.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.3% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM151" t="inlineStr">
@@ -41271,104 +41271,104 @@
       </c>
       <c r="AN151" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>37.78</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>87.73</t>
+          <t>88.53</t>
         </is>
       </c>
       <c r="AQ151" t="inlineStr">
         <is>
-          <t>99.464</t>
+          <t>99.7938</t>
         </is>
       </c>
       <c r="AR151" t="inlineStr">
         <is>
-          <t>0.3974</t>
+          <t>0.3559</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr">
         <is>
-          <t>0.1683</t>
+          <t>0.1275</t>
         </is>
       </c>
       <c r="AT151" t="inlineStr">
         <is>
-          <t>0.2969</t>
+          <t>0.2711</t>
         </is>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>73.71</t>
+          <t>71.03</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>36.67</t>
+          <t>13.75</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>41.78</t>
+          <t>41.74</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>24.81</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>0.1882</t>
+          <t>0.1294</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>37.16</t>
+          <t>41.51</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>88.06</t>
+          <t>88.99</t>
         </is>
       </c>
       <c r="BD151" t="inlineStr">
         <is>
-          <t>0.4213</t>
+          <t>0.3993</t>
         </is>
       </c>
       <c r="BE151" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1534</t>
         </is>
       </c>
       <c r="BF151" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>23.37</t>
         </is>
       </c>
       <c r="BG151" t="inlineStr"/>
       <c r="BH151" t="inlineStr"/>
       <c r="BI151" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ151" t="inlineStr"/>
@@ -41379,27 +41379,27 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>605170</t>
+          <t>662139</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Victor Caratini</t>
+          <t>Daulton Varsho</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-09-20T20:07:00Z</t>
+          <t>2026-09-20T18:10:00Z</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -41409,22 +41409,22 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Ryan Johnson</t>
+          <t>Martín Pérez</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>696270</t>
+          <t>527048</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L152" t="n">
@@ -41442,26 +41442,26 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P152" t="n">
-        <v>29.6</v>
+        <v>35.9</v>
       </c>
       <c r="Q152" t="n">
-        <v>44.6</v>
+        <v>37.7</v>
       </c>
       <c r="R152" t="n">
-        <v>28.2</v>
+        <v>27.6</v>
       </c>
       <c r="S152" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T152" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U152" t="n">
-        <v>13.6</v>
+        <v>18.3</v>
       </c>
       <c r="V152" t="inlineStr">
         <is>
@@ -41475,7 +41475,7 @@
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y152" t="inlineStr">
@@ -41517,134 +41517,134 @@
       </c>
       <c r="AH152" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/19, 0 HR</t>
+          <t>Last 7 games: 2/24, 1 HR</t>
         </is>
       </c>
       <c r="AL152" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.5% barrel, 13.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.9% barrel, 10.9 HR allowed</t>
         </is>
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN152" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>37.78</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>89.19</t>
+          <t>87.73</t>
         </is>
       </c>
       <c r="AQ152" t="inlineStr">
         <is>
-          <t>98.9527</t>
+          <t>99.464</t>
         </is>
       </c>
       <c r="AR152" t="inlineStr">
         <is>
-          <t>0.3844</t>
+          <t>0.3974</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr">
         <is>
-          <t>0.1476</t>
+          <t>0.1683</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.2969</t>
         </is>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>71.39</t>
+          <t>73.71</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>16.29</t>
+          <t>36.67</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>37.71</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>23.06</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>0.1107</t>
+          <t>0.1882</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>9.48</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>36.42</t>
+          <t>37.16</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>87.68</t>
+          <t>88.06</t>
         </is>
       </c>
       <c r="BD152" t="inlineStr">
         <is>
-          <t>0.4332</t>
+          <t>0.4213</t>
         </is>
       </c>
       <c r="BE152" t="inlineStr">
         <is>
-          <t>0.1833</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="BF152" t="inlineStr">
         <is>
-          <t>34.09</t>
+          <t>24.69</t>
         </is>
       </c>
       <c r="BG152" t="inlineStr"/>
       <c r="BH152" t="inlineStr"/>
       <c r="BI152" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ152" t="inlineStr"/>
@@ -54973,7 +54973,7 @@
         <v>50</v>
       </c>
       <c r="U202" t="n">
-        <v>39.2</v>
+        <v>37.8</v>
       </c>
       <c r="V202" t="inlineStr">
         <is>
@@ -55034,7 +55034,7 @@
       </c>
       <c r="AI202" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ202" t="inlineStr">
@@ -55044,7 +55044,7 @@
       </c>
       <c r="AK202" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 1 HR</t>
+          <t>Last 7 games: 7/28, 1 HR</t>
         </is>
       </c>
       <c r="AL202" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-09-20.xlsx
+++ b/outputs/daily/hr_rankings_2026-09-20.xlsx
@@ -5013,7 +5013,7 @@
         <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>40.1</v>
+        <v>39.1</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -6100,7 +6100,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>57.3</v>
+        <v>57.2</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>50</v>
       </c>
       <c r="U21" t="n">
-        <v>22.9</v>
+        <v>21.1</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/22, 0 HR</t>
+          <t>Last 7 games: 6/23, 0 HR</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -9411,27 +9411,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>663457</t>
+          <t>671732</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lars Nootbaar</t>
+          <t>Lawrence Butler</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-20T20:10:00Z</t>
+          <t>2026-09-20T17:40:00Z</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9441,17 +9441,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Will Warren</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>701542</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -9460,7 +9460,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>55.9</v>
+        <v>55.8</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -9474,54 +9474,58 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>47.5</v>
+        <v>37.2</v>
       </c>
       <c r="Q33" t="n">
-        <v>49.2</v>
+        <v>54.2</v>
       </c>
       <c r="R33" t="n">
-        <v>42.2</v>
+        <v>40.6</v>
       </c>
       <c r="S33" t="n">
-        <v>93.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T33" t="n">
         <v>80</v>
       </c>
       <c r="U33" t="n">
-        <v>36.3</v>
+        <v>74.5</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="Y33" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9546,22 +9550,22 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.6% barrel, 21.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.6% barrel, 25.8 HR allowed</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
@@ -9571,112 +9575,112 @@
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>8.57</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>44.61</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>91.86</t>
+          <t>89.94</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>101.7802</t>
+          <t>101.8414</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>0.4231</t>
+          <t>0.3947</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>0.1809</t>
+          <t>0.1563</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>0.3331</t>
+          <t>0.319</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>73.26</t>
+          <t>73.63</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>35.33</t>
+          <t>38.02</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>38.77</t>
+          <t>35.52</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>28.2</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>0.1616</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>44.67</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>90.93</t>
+          <t>90.12</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>0.4169</t>
+          <t>0.3973</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>0.1747</t>
         </is>
       </c>
       <c r="BF33" t="inlineStr">
         <is>
-          <t>23.96</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="BG33" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ33" t="inlineStr"/>
@@ -9687,27 +9691,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>671732</t>
+          <t>665487</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lawrence Butler</t>
+          <t>Fernando Tatis Jr.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-20T17:40:00Z</t>
+          <t>2026-09-20T20:10:00Z</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9717,17 +9721,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Sandy Alcantara</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>645261</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -9750,26 +9754,26 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>37.2</v>
+        <v>58</v>
       </c>
       <c r="Q34" t="n">
-        <v>54.2</v>
+        <v>36.9</v>
       </c>
       <c r="R34" t="n">
-        <v>40.6</v>
+        <v>47.1</v>
       </c>
       <c r="S34" t="n">
-        <v>96.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T34" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U34" t="n">
-        <v>74.5</v>
+        <v>63.8</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -9783,7 +9787,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -9821,12 +9825,12 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
@@ -9841,122 +9845,122 @@
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.6% barrel, 25.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.6% barrel, 22.7 HR allowed</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>8.57</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>44.61</t>
+          <t>53.13</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>89.94</t>
+          <t>93.09</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>101.8414</t>
+          <t>104.4668</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>0.3947</t>
+          <t>0.495</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>0.1563</t>
+          <t>0.2072</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>0.3756</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>73.63</t>
+          <t>75.65</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>38.02</t>
+          <t>58.12</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>35.52</t>
+          <t>34.73</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>0.1616</t>
+          <t>0.1787</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>38.77</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>90.12</t>
+          <t>89.23</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>0.3973</t>
+          <t>0.3982</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
-          <t>0.1747</t>
+          <t>0.1428</t>
         </is>
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="BG34" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ34" t="inlineStr"/>
@@ -9967,22 +9971,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>665487</t>
+          <t>663457</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Fernando Tatis Jr.</t>
+          <t>Lars Nootbaar</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -10002,12 +10006,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Sandy Alcantara</t>
+          <t>Will Warren</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>645261</t>
+          <t>701542</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -10030,50 +10034,42 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>58</v>
+        <v>47.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>36.9</v>
+        <v>49.2</v>
       </c>
       <c r="R35" t="n">
-        <v>47.1</v>
+        <v>42.2</v>
       </c>
       <c r="S35" t="n">
         <v>93.2</v>
       </c>
       <c r="T35" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U35" t="n">
-        <v>63.8</v>
+        <v>34.9</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -10081,7 +10077,11 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC35" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10101,142 +10101,142 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.6% barrel, 22.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.6% barrel, 21.3 HR allowed</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>12.26</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>53.13</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>93.09</t>
+          <t>91.86</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>104.4668</t>
+          <t>101.7802</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>0.495</t>
+          <t>0.4231</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>0.2072</t>
+          <t>0.1809</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>0.3756</t>
+          <t>0.3331</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>75.65</t>
+          <t>73.26</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>58.12</t>
+          <t>35.33</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>34.73</t>
+          <t>38.77</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>0.1787</t>
+          <t>0.134</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>8.59</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>38.77</t>
+          <t>44.67</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>89.23</t>
+          <t>90.93</t>
         </is>
       </c>
       <c r="BD35" t="inlineStr">
         <is>
-          <t>0.3982</t>
+          <t>0.4169</t>
         </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
-          <t>0.1428</t>
+          <t>0.161</t>
         </is>
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>23.96</t>
         </is>
       </c>
       <c r="BG35" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr"/>
@@ -11449,7 +11449,7 @@
         <v>75</v>
       </c>
       <c r="U40" t="n">
-        <v>15.3</v>
+        <v>14.1</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -11502,7 +11502,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
@@ -11512,7 +11512,7 @@
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 6/28, 0 HR</t>
         </is>
       </c>
       <c r="AL40" t="inlineStr">
@@ -12536,7 +12536,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>54.4</v>
+        <v>54.3</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         <v>50</v>
       </c>
       <c r="U44" t="n">
-        <v>33.9</v>
+        <v>32</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -12636,7 +12636,7 @@
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Contact streak: 9/26 over last 7 games</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL44" t="inlineStr">
@@ -13887,47 +13887,47 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>608369</t>
+          <t>686948</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Corey Seager</t>
+          <t>Drake Baldwin</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-20T18:35:00Z</t>
+          <t>2026-09-20T18:10:00Z</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Spencer Miles</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>693686</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -13936,7 +13936,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>53.2</v>
+        <v>53.1</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -13954,22 +13954,22 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>61.8</v>
+        <v>56.1</v>
       </c>
       <c r="Q49" t="n">
-        <v>11.9</v>
+        <v>21.9</v>
       </c>
       <c r="R49" t="n">
-        <v>42.1</v>
+        <v>41.6</v>
       </c>
       <c r="S49" t="n">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="T49" t="n">
         <v>80</v>
       </c>
       <c r="U49" t="n">
-        <v>48.5</v>
+        <v>57.2</v>
       </c>
       <c r="V49" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -14004,7 +14004,7 @@
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr"/>
@@ -14021,12 +14021,12 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -14036,112 +14036,112 @@
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Contact streak: 9/28 over last 7 games</t>
+          <t>Contact streak: 11/29 over last 7 games</t>
         </is>
       </c>
       <c r="AL49" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 3.5% barrel, 5.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.1% barrel, 12.8 HR allowed</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>14.67</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>49.89</t>
+          <t>50.16</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>92.13</t>
+          <t>91.49</t>
         </is>
       </c>
       <c r="AQ49" t="inlineStr">
         <is>
-          <t>102.614</t>
+          <t>102.1395</t>
         </is>
       </c>
       <c r="AR49" t="inlineStr">
         <is>
-          <t>0.5095</t>
+          <t>0.4947</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr">
         <is>
-          <t>0.2462</t>
+          <t>0.2185</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr">
         <is>
-          <t>0.3678</t>
+          <t>0.3635</t>
         </is>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>56.51</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>40.57</t>
+          <t>32.36</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>0.2034</t>
+          <t>0.1817</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.31</t>
         </is>
       </c>
       <c r="BD49" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.3229</t>
         </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>0.1192</t>
         </is>
       </c>
       <c r="BF49" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="BG49" t="inlineStr">
@@ -14151,12 +14151,12 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI49" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ49" t="inlineStr"/>
@@ -14167,47 +14167,47 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>686948</t>
+          <t>608369</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Drake Baldwin</t>
+          <t>Corey Seager</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-20T18:10:00Z</t>
+          <t>2026-09-20T18:35:00Z</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Game Over</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Spencer Miles</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>693686</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -14234,22 +14234,22 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>56.1</v>
+        <v>61.8</v>
       </c>
       <c r="Q50" t="n">
-        <v>21.9</v>
+        <v>11.9</v>
       </c>
       <c r="R50" t="n">
-        <v>41.6</v>
+        <v>42.1</v>
       </c>
       <c r="S50" t="n">
-        <v>93.2</v>
+        <v>100</v>
       </c>
       <c r="T50" t="n">
         <v>80</v>
       </c>
       <c r="U50" t="n">
-        <v>57.2</v>
+        <v>46.9</v>
       </c>
       <c r="V50" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
@@ -14284,7 +14284,7 @@
       <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr"/>
@@ -14301,7 +14301,7 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr">
@@ -14316,112 +14316,112 @@
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Contact streak: 11/29 over last 7 games</t>
+          <t>Last 7 games: 9/29, 1 HR</t>
         </is>
       </c>
       <c r="AL50" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.1% barrel, 12.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 3.5% barrel, 5.0 HR allowed</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>12.26</t>
+          <t>14.67</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>50.16</t>
+          <t>49.89</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>91.49</t>
+          <t>92.13</t>
         </is>
       </c>
       <c r="AQ50" t="inlineStr">
         <is>
-          <t>102.1395</t>
+          <t>102.614</t>
         </is>
       </c>
       <c r="AR50" t="inlineStr">
         <is>
-          <t>0.4947</t>
+          <t>0.5095</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>0.2185</t>
+          <t>0.2462</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr">
         <is>
-          <t>0.3635</t>
+          <t>0.3678</t>
         </is>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>56.51</t>
+          <t>15.16</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>32.36</t>
+          <t>40.57</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>0.1817</t>
+          <t>0.2034</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>86.31</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="BD50" t="inlineStr">
         <is>
-          <t>0.3229</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
-          <t>0.1192</t>
+          <t>0.091</t>
         </is>
       </c>
       <c r="BF50" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="BG50" t="inlineStr">
@@ -14431,12 +14431,12 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI50" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ50" t="inlineStr"/>
@@ -14809,7 +14809,7 @@
         <v>50</v>
       </c>
       <c r="U52" t="n">
-        <v>10.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
@@ -14866,7 +14866,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
@@ -14876,7 +14876,7 @@
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 0 HR</t>
+          <t>Last 7 games: 4/22, 0 HR</t>
         </is>
       </c>
       <c r="AL52" t="inlineStr">
@@ -24243,12 +24243,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>672640</t>
+          <t>805300</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Otto Lopez</t>
+          <t>Jakob Marsee</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -24273,7 +24273,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -24306,11 +24306,11 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P86" t="n">
-        <v>30.1</v>
+        <v>20.8</v>
       </c>
       <c r="Q86" t="n">
         <v>43</v>
@@ -24319,13 +24319,13 @@
         <v>47.1</v>
       </c>
       <c r="S86" t="n">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T86" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U86" t="n">
-        <v>34.9</v>
+        <v>81.7</v>
       </c>
       <c r="V86" t="inlineStr">
         <is>
@@ -24339,7 +24339,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y86" t="inlineStr">
@@ -24377,27 +24377,27 @@
       </c>
       <c r="AH86" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL86" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.6% barrel, 20.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.6% barrel, 20.6 HR allowed</t>
         </is>
       </c>
       <c r="AM86" t="inlineStr">
@@ -24407,67 +24407,67 @@
       </c>
       <c r="AN86" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>36.99</t>
         </is>
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>88.99</t>
+          <t>87.78</t>
         </is>
       </c>
       <c r="AQ86" t="inlineStr">
         <is>
-          <t>100.1719</t>
+          <t>98.6208</t>
         </is>
       </c>
       <c r="AR86" t="inlineStr">
         <is>
-          <t>0.4242</t>
+          <t>0.3657</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr">
         <is>
-          <t>0.1468</t>
+          <t>0.1204</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr">
         <is>
-          <t>0.3286</t>
+          <t>0.3239</t>
         </is>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>71.84</t>
+          <t>70.36</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>33.63</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.19</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>0.1325</t>
+          <t>0.1461</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
@@ -24523,27 +24523,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>805300</t>
+          <t>686797</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Jakob Marsee</t>
+          <t>Brooks Lee</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-09-20T20:10:00Z</t>
+          <t>2026-09-20T20:07:00Z</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -24553,17 +24553,17 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Walker Buehler</t>
+          <t>Ryan Johnson</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>621111</t>
+          <t>696270</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -24572,7 +24572,7 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>47.6</v>
+        <v>47.5</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
@@ -24586,26 +24586,26 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>20.8</v>
+        <v>21.3</v>
       </c>
       <c r="Q87" t="n">
-        <v>43</v>
+        <v>44.6</v>
       </c>
       <c r="R87" t="n">
-        <v>47.1</v>
+        <v>49.7</v>
       </c>
       <c r="S87" t="n">
-        <v>86.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="T87" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U87" t="n">
-        <v>81.7</v>
+        <v>32</v>
       </c>
       <c r="V87" t="inlineStr">
         <is>
@@ -24619,7 +24619,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
@@ -24657,142 +24657,142 @@
       </c>
       <c r="AH87" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 8/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL87" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.6% barrel, 20.6 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.5% barrel, 13.8 HR allowed</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>36.99</t>
+          <t>35.28</t>
         </is>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>87.78</t>
+          <t>88.25</t>
         </is>
       </c>
       <c r="AQ87" t="inlineStr">
         <is>
-          <t>98.6208</t>
+          <t>97.71</t>
         </is>
       </c>
       <c r="AR87" t="inlineStr">
         <is>
-          <t>0.3657</t>
+          <t>0.3558</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>0.1204</t>
+          <t>0.1267</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr">
         <is>
-          <t>0.3239</t>
+          <t>0.2792</t>
         </is>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>69.92</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>8.42</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>41.71</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>23.19</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>0.1461</t>
+          <t>0.1641</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>9.48</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>36.42</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
         <is>
-          <t>88.88</t>
+          <t>87.68</t>
         </is>
       </c>
       <c r="BD87" t="inlineStr">
         <is>
-          <t>0.4171</t>
+          <t>0.4332</t>
         </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
-          <t>0.1645</t>
+          <t>0.1833</t>
         </is>
       </c>
       <c r="BF87" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>34.09</t>
         </is>
       </c>
       <c r="BG87" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI87" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ87" t="inlineStr"/>
@@ -24803,27 +24803,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>686797</t>
+          <t>672640</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Brooks Lee</t>
+          <t>Otto Lopez</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-09-20T20:07:00Z</t>
+          <t>2026-09-20T20:10:00Z</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -24838,12 +24838,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Ryan Johnson</t>
+          <t>Walker Buehler</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>696270</t>
+          <t>621111</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -24866,26 +24866,26 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>21.3</v>
+        <v>30.1</v>
       </c>
       <c r="Q88" t="n">
-        <v>44.6</v>
+        <v>43</v>
       </c>
       <c r="R88" t="n">
-        <v>49.7</v>
+        <v>47.1</v>
       </c>
       <c r="S88" t="n">
         <v>100</v>
       </c>
       <c r="T88" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U88" t="n">
-        <v>32</v>
+        <v>33.7</v>
       </c>
       <c r="V88" t="inlineStr">
         <is>
@@ -24937,142 +24937,142 @@
       </c>
       <c r="AH88" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Contact streak: 8/24 over last 7 games</t>
+          <t>Last 7 games: 6/27, 1 HR</t>
         </is>
       </c>
       <c r="AL88" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.5% barrel, 13.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.6% barrel, 20.6 HR allowed</t>
         </is>
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>35.28</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>88.25</t>
+          <t>88.99</t>
         </is>
       </c>
       <c r="AQ88" t="inlineStr">
         <is>
-          <t>97.71</t>
+          <t>100.1719</t>
         </is>
       </c>
       <c r="AR88" t="inlineStr">
         <is>
-          <t>0.3558</t>
+          <t>0.4242</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr">
         <is>
-          <t>0.1267</t>
+          <t>0.1468</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr">
         <is>
-          <t>0.2792</t>
+          <t>0.3286</t>
         </is>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>69.92</t>
+          <t>71.84</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>8.42</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>41.71</t>
+          <t>33.63</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>0.1641</t>
+          <t>0.1325</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>9.48</t>
+          <t>8.59</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>36.42</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>87.68</t>
+          <t>88.88</t>
         </is>
       </c>
       <c r="BD88" t="inlineStr">
         <is>
-          <t>0.4332</t>
+          <t>0.4171</t>
         </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
-          <t>0.1833</t>
+          <t>0.1645</t>
         </is>
       </c>
       <c r="BF88" t="inlineStr">
         <is>
-          <t>34.09</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="BG88" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BI88" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ88" t="inlineStr"/>
@@ -25692,7 +25692,7 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>47.3</v>
+        <v>47.2</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>50</v>
       </c>
       <c r="U91" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="V91" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ91" t="inlineStr">
@@ -25792,7 +25792,7 @@
       </c>
       <c r="AK91" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/25, 0 HR</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AL91" t="inlineStr">
@@ -29003,52 +29003,52 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>668800</t>
+          <t>687401</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Andrew Knizner</t>
+          <t>Joey Ortiz</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-09-20T20:10:00Z</t>
+          <t>2026-09-20T23:20:00Z</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Jack Dreyer</t>
+          <t>Brandon Young</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>676263</t>
+          <t>687064</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L103" t="n">
@@ -29066,26 +29066,26 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P103" t="n">
-        <v>13.4</v>
+        <v>16.9</v>
       </c>
       <c r="Q103" t="n">
-        <v>34.3</v>
+        <v>43.1</v>
       </c>
       <c r="R103" t="n">
-        <v>63.1</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S103" t="n">
-        <v>94.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T103" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U103" t="n">
-        <v>58.7</v>
+        <v>54.9</v>
       </c>
       <c r="V103" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y103" t="inlineStr">
@@ -29137,12 +29137,12 @@
       </c>
       <c r="AH103" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ103" t="inlineStr">
@@ -29152,12 +29152,12 @@
       </c>
       <c r="AK103" t="inlineStr">
         <is>
-          <t>Contact streak: 7/18 over last 7 games</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL103" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 6.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.8% barrel, 18.3 HR allowed</t>
         </is>
       </c>
       <c r="AM103" t="inlineStr">
@@ -29167,112 +29167,112 @@
       </c>
       <c r="AN103" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>35.6</t>
         </is>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>85.53</t>
+          <t>87.77</t>
         </is>
       </c>
       <c r="AQ103" t="inlineStr">
         <is>
-          <t>97.1405</t>
+          <t>99.1565</t>
         </is>
       </c>
       <c r="AR103" t="inlineStr">
         <is>
-          <t>0.3454</t>
+          <t>0.3424</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr">
         <is>
-          <t>0.1176</t>
+          <t>0.0981</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr">
         <is>
-          <t>0.2899</t>
+          <t>0.2918</t>
         </is>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>69.69</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>6.42</t>
+          <t>30.64</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>31.98</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>23.34</t>
+          <t>20.03</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>0.1319</t>
+          <t>0.122</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>40.17</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>89.88</t>
+          <t>89.33</t>
         </is>
       </c>
       <c r="BD103" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.4159</t>
         </is>
       </c>
       <c r="BE103" t="inlineStr">
         <is>
-          <t>0.1377</t>
+          <t>0.1651</t>
         </is>
       </c>
       <c r="BF103" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>26.73</t>
         </is>
       </c>
       <c r="BG103" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH103" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BI103" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ103" t="inlineStr"/>
@@ -29283,56 +29283,56 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>687401</t>
+          <t>668800</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Andrew Knizner</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-09-20T23:20:00Z</t>
+          <t>2026-09-20T20:10:00Z</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Brandon Young</t>
+          <t>Jack Dreyer</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>687064</t>
+          <t>676263</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>45.4</v>
+        <v>45.2</v>
       </c>
       <c r="M104" t="inlineStr">
         <is>
@@ -29346,26 +29346,26 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P104" t="n">
-        <v>16.9</v>
+        <v>13.4</v>
       </c>
       <c r="Q104" t="n">
-        <v>43.1</v>
+        <v>34.3</v>
       </c>
       <c r="R104" t="n">
-        <v>67.59999999999999</v>
+        <v>63.1</v>
       </c>
       <c r="S104" t="n">
-        <v>86.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T104" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U104" t="n">
-        <v>54.9</v>
+        <v>55.6</v>
       </c>
       <c r="V104" t="inlineStr">
         <is>
@@ -29379,7 +29379,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y104" t="inlineStr">
@@ -29417,12 +29417,12 @@
       </c>
       <c r="AH104" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ104" t="inlineStr">
@@ -29432,12 +29432,12 @@
       </c>
       <c r="AK104" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Contact streak: 7/19 over last 7 games</t>
         </is>
       </c>
       <c r="AL104" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.8% barrel, 18.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 6.1 HR allowed</t>
         </is>
       </c>
       <c r="AM104" t="inlineStr">
@@ -29447,112 +29447,112 @@
       </c>
       <c r="AN104" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>35.6</t>
+          <t>29.29</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>87.77</t>
+          <t>85.53</t>
         </is>
       </c>
       <c r="AQ104" t="inlineStr">
         <is>
-          <t>99.1565</t>
+          <t>97.1405</t>
         </is>
       </c>
       <c r="AR104" t="inlineStr">
         <is>
-          <t>0.3424</t>
+          <t>0.3454</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr">
         <is>
-          <t>0.0981</t>
+          <t>0.1176</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr">
         <is>
-          <t>0.2918</t>
+          <t>0.2899</t>
         </is>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>69.69</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>30.64</t>
+          <t>6.42</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>31.98</t>
+          <t>31.03</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>23.34</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.1319</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>40.17</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>89.33</t>
+          <t>89.88</t>
         </is>
       </c>
       <c r="BD104" t="inlineStr">
         <is>
-          <t>0.4159</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
-          <t>0.1651</t>
+          <t>0.1377</t>
         </is>
       </c>
       <c r="BF104" t="inlineStr">
         <is>
-          <t>26.73</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="BG104" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH104" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI104" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ104" t="inlineStr"/>
@@ -35435,47 +35435,47 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>673962</t>
+          <t>573262</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Josh Jung</t>
+          <t>Mike Yastrzemski</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-09-20T18:35:00Z</t>
+          <t>2026-09-20T18:10:00Z</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Spencer Miles</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>693686</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -35484,7 +35484,7 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="M126" t="inlineStr">
         <is>
@@ -35498,26 +35498,26 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P126" t="n">
-        <v>37.2</v>
+        <v>34.2</v>
       </c>
       <c r="Q126" t="n">
-        <v>11.9</v>
+        <v>21.9</v>
       </c>
       <c r="R126" t="n">
-        <v>42.1</v>
+        <v>41.6</v>
       </c>
       <c r="S126" t="n">
-        <v>96.59999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="T126" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U126" t="n">
-        <v>63.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="V126" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y126" t="inlineStr">
@@ -35552,7 +35552,7 @@
       <c r="AB126" t="inlineStr"/>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD126" t="inlineStr"/>
@@ -35569,27 +35569,27 @@
       </c>
       <c r="AH126" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL126" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 3.5% barrel, 5.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.1% barrel, 12.8 HR allowed</t>
         </is>
       </c>
       <c r="AM126" t="inlineStr">
@@ -35599,97 +35599,97 @@
       </c>
       <c r="AN126" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>48.24</t>
+          <t>42.32</t>
         </is>
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>90.21</t>
+          <t>90.38</t>
         </is>
       </c>
       <c r="AQ126" t="inlineStr">
         <is>
-          <t>100.402</t>
+          <t>99.7373</t>
         </is>
       </c>
       <c r="AR126" t="inlineStr">
         <is>
-          <t>0.4329</t>
+          <t>0.3819</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr">
         <is>
-          <t>0.1585</t>
+          <t>0.1463</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr">
         <is>
-          <t>0.3355</t>
+          <t>0.3136</t>
         </is>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>71.31</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>8.58</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>37.55</t>
+          <t>44.22</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>23.71</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>0.1509</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.31</t>
         </is>
       </c>
       <c r="BD126" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.3229</t>
         </is>
       </c>
       <c r="BE126" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>0.1192</t>
         </is>
       </c>
       <c r="BF126" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="BG126" t="inlineStr">
@@ -35699,12 +35699,12 @@
       </c>
       <c r="BH126" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI126" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ126" t="inlineStr"/>
@@ -35715,47 +35715,47 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>573262</t>
+          <t>673962</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Mike Yastrzemski</t>
+          <t>Josh Jung</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-09-20T18:10:00Z</t>
+          <t>2026-09-20T18:35:00Z</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Game Over</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Spencer Miles</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>693686</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -35778,26 +35778,26 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P127" t="n">
-        <v>34.2</v>
+        <v>37.2</v>
       </c>
       <c r="Q127" t="n">
-        <v>21.9</v>
+        <v>11.9</v>
       </c>
       <c r="R127" t="n">
-        <v>41.6</v>
+        <v>42.1</v>
       </c>
       <c r="S127" t="n">
-        <v>64.3</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T127" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U127" t="n">
-        <v>71.09999999999999</v>
+        <v>61.5</v>
       </c>
       <c r="V127" t="inlineStr">
         <is>
@@ -35811,7 +35811,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y127" t="inlineStr">
@@ -35832,7 +35832,7 @@
       <c r="AB127" t="inlineStr"/>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD127" t="inlineStr"/>
@@ -35849,27 +35849,27 @@
       </c>
       <c r="AH127" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL127" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.1% barrel, 12.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 3.5% barrel, 5.0 HR allowed</t>
         </is>
       </c>
       <c r="AM127" t="inlineStr">
@@ -35879,97 +35879,97 @@
       </c>
       <c r="AN127" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>42.32</t>
+          <t>48.24</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>90.38</t>
+          <t>90.21</t>
         </is>
       </c>
       <c r="AQ127" t="inlineStr">
         <is>
-          <t>99.7373</t>
+          <t>100.402</t>
         </is>
       </c>
       <c r="AR127" t="inlineStr">
         <is>
-          <t>0.3819</t>
+          <t>0.4329</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr">
         <is>
-          <t>0.1463</t>
+          <t>0.1585</t>
         </is>
       </c>
       <c r="AT127" t="inlineStr">
         <is>
-          <t>0.3136</t>
+          <t>0.3355</t>
         </is>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>71.31</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>8.58</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>44.22</t>
+          <t>37.55</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>23.71</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>12.8</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>0.1595</t>
+          <t>0.1509</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>86.31</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="BD127" t="inlineStr">
         <is>
-          <t>0.3229</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="BE127" t="inlineStr">
         <is>
-          <t>0.1192</t>
+          <t>0.091</t>
         </is>
       </c>
       <c r="BF127" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="BG127" t="inlineStr">
@@ -35979,12 +35979,12 @@
       </c>
       <c r="BH127" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI127" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ127" t="inlineStr"/>
@@ -36555,24 +36555,24 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>683011</t>
+          <t>694374</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Anthony Volpe</t>
+          <t>Tim Tawa</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
           <t>NYY</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
       <c r="F130" t="inlineStr">
         <is>
           <t>2026-09-20T20:10:00Z</t>
@@ -36585,17 +36585,17 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Corbin Burnes</t>
+          <t>Will Warren</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>669203</t>
+          <t>701542</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -36618,50 +36618,42 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P130" t="n">
-        <v>25.5</v>
+        <v>40.2</v>
       </c>
       <c r="Q130" t="n">
-        <v>54.5</v>
+        <v>49.2</v>
       </c>
       <c r="R130" t="n">
         <v>42.2</v>
       </c>
       <c r="S130" t="n">
-        <v>64.3</v>
+        <v>44.8</v>
       </c>
       <c r="T130" t="n">
         <v>50</v>
       </c>
       <c r="U130" t="n">
-        <v>17.7</v>
+        <v>0</v>
       </c>
       <c r="V130" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W130" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X130" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="W130" t="inlineStr"/>
+      <c r="X130" t="inlineStr"/>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -36669,7 +36661,11 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB130" t="inlineStr"/>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC130" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -36689,7 +36685,7 @@
       </c>
       <c r="AH130" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI130" t="inlineStr">
@@ -36704,112 +36700,112 @@
       </c>
       <c r="AK130" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/21, 0 HR</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AL130" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.2% barrel, 3.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.6% barrel, 21.3 HR allowed</t>
         </is>
       </c>
       <c r="AM130" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN130" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>38.47</t>
+          <t>43.29</t>
         </is>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>88.46</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="AQ130" t="inlineStr">
         <is>
-          <t>98.8902</t>
+          <t>100.6567</t>
         </is>
       </c>
       <c r="AR130" t="inlineStr">
         <is>
-          <t>0.3581</t>
+          <t>0.3932</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>0.1613</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr">
         <is>
-          <t>0.2982</t>
+          <t>0.304</t>
         </is>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>71.62</t>
+          <t>73.66</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>19.19</t>
+          <t>34.88</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>33.01</t>
+          <t>38.77</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>24.83</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>0.1195</t>
+          <t>0.1509</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>11.18</t>
+          <t>8.59</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>38.73</t>
+          <t>44.67</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>90.34</t>
+          <t>90.93</t>
         </is>
       </c>
       <c r="BD130" t="inlineStr">
         <is>
-          <t>0.4081</t>
+          <t>0.4169</t>
         </is>
       </c>
       <c r="BE130" t="inlineStr">
         <is>
-          <t>0.1839</t>
+          <t>0.161</t>
         </is>
       </c>
       <c r="BF130" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>23.96</t>
         </is>
       </c>
       <c r="BG130" t="inlineStr">
@@ -36835,24 +36831,24 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>694374</t>
+          <t>683011</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Tim Tawa</t>
+          <t>Anthony Volpe</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
       <c r="F131" t="inlineStr">
         <is>
           <t>2026-09-20T20:10:00Z</t>
@@ -36865,17 +36861,17 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Will Warren</t>
+          <t>Corbin Burnes</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>701542</t>
+          <t>669203</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -36884,7 +36880,7 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="M131" t="inlineStr">
         <is>
@@ -36898,54 +36894,58 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P131" t="n">
-        <v>40.2</v>
+        <v>25.5</v>
       </c>
       <c r="Q131" t="n">
-        <v>49.2</v>
+        <v>54.5</v>
       </c>
       <c r="R131" t="n">
         <v>42.2</v>
       </c>
       <c r="S131" t="n">
-        <v>44.8</v>
+        <v>64.3</v>
       </c>
       <c r="T131" t="n">
         <v>50</v>
       </c>
       <c r="U131" t="n">
-        <v>0</v>
+        <v>16.1</v>
       </c>
       <c r="V131" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W131" t="inlineStr"/>
-      <c r="X131" t="inlineStr"/>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="Y131" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB131" t="inlineStr"/>
       <c r="AC131" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -36965,12 +36965,12 @@
       </c>
       <c r="AH131" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ131" t="inlineStr">
@@ -36980,112 +36980,112 @@
       </c>
       <c r="AK131" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 5/22, 0 HR</t>
         </is>
       </c>
       <c r="AL131" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.6% barrel, 21.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.2% barrel, 3.5 HR allowed</t>
         </is>
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN131" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>6.37</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>43.29</t>
+          <t>38.47</t>
         </is>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>88.46</t>
         </is>
       </c>
       <c r="AQ131" t="inlineStr">
         <is>
-          <t>100.6567</t>
+          <t>98.8902</t>
         </is>
       </c>
       <c r="AR131" t="inlineStr">
         <is>
-          <t>0.3932</t>
+          <t>0.3581</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr">
         <is>
-          <t>0.1613</t>
+          <t>0.126</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>0.2982</t>
         </is>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>73.66</t>
+          <t>71.62</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>34.88</t>
+          <t>19.19</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>38.77</t>
+          <t>33.01</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>24.83</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>0.1509</t>
+          <t>0.1195</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>11.18</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>44.67</t>
+          <t>38.73</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>90.93</t>
+          <t>90.34</t>
         </is>
       </c>
       <c r="BD131" t="inlineStr">
         <is>
-          <t>0.4169</t>
+          <t>0.4081</t>
         </is>
       </c>
       <c r="BE131" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>0.1839</t>
         </is>
       </c>
       <c r="BF131" t="inlineStr">
         <is>
-          <t>23.96</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="BG131" t="inlineStr">
@@ -38000,7 +38000,7 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>41.8</v>
+        <v>41.7</v>
       </c>
       <c r="M135" t="inlineStr">
         <is>
@@ -38033,7 +38033,7 @@
         <v>78</v>
       </c>
       <c r="U135" t="n">
-        <v>15.3</v>
+        <v>13.6</v>
       </c>
       <c r="V135" t="inlineStr">
         <is>
@@ -38090,7 +38090,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ135" t="inlineStr">
@@ -38100,7 +38100,7 @@
       </c>
       <c r="AK135" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/18, 0 HR</t>
+          <t>Last 7 games: 4/19, 0 HR</t>
         </is>
       </c>
       <c r="AL135" t="inlineStr">
@@ -38231,32 +38231,32 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>676439</t>
+          <t>807726</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Hunter Feduccia</t>
+          <t>John Peck</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-09-20T20:10:00Z</t>
+          <t>2026-09-20T18:10:00Z</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Delayed Start</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -38266,21 +38266,21 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Matt Wilkinson</t>
+          <t>Davis Martin</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>683363</t>
+          <t>663436</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="M136" t="inlineStr">
         <is>
@@ -38294,17 +38294,17 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P136" t="n">
-        <v>27.1</v>
+        <v>34.4</v>
       </c>
       <c r="Q136" t="n">
-        <v>50.9</v>
+        <v>44.8</v>
       </c>
       <c r="R136" t="n">
-        <v>63.1</v>
+        <v>53.6</v>
       </c>
       <c r="S136" t="n">
         <v>44.8</v>
@@ -38313,7 +38313,7 @@
         <v>50</v>
       </c>
       <c r="U136" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="V136" t="inlineStr">
         <is>
@@ -38348,7 +38348,7 @@
       <c r="AB136" t="inlineStr"/>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD136" t="inlineStr"/>
@@ -38365,12 +38365,12 @@
       </c>
       <c r="AH136" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ136" t="inlineStr">
@@ -38380,127 +38380,127 @@
       </c>
       <c r="AK136" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/15, 0 HR</t>
+          <t>Last 7 games: 3/17, 0 HR</t>
         </is>
       </c>
       <c r="AL136" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.7% barrel, 4.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.4% barrel, 15.8 HR allowed</t>
         </is>
       </c>
       <c r="AM136" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN136" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AQ136" t="inlineStr">
         <is>
-          <t>98.7756</t>
+          <t>98.866</t>
         </is>
       </c>
       <c r="AR136" t="inlineStr">
         <is>
-          <t>0.3475</t>
+          <t>0.383</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr">
         <is>
-          <t>0.1206</t>
+          <t>0.142</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr">
         <is>
-          <t>0.3058</t>
+          <t>0.341</t>
         </is>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>70.71</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>12.56</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>32.73</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>26.89</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>0.021</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>44.67</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.42</t>
         </is>
       </c>
       <c r="BD136" t="inlineStr">
         <is>
-          <t>0.444</t>
+          <t>0.4293</t>
         </is>
       </c>
       <c r="BE136" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>0.1573</t>
         </is>
       </c>
       <c r="BF136" t="inlineStr">
         <is>
-          <t>32.3</t>
+          <t>23.97</t>
         </is>
       </c>
       <c r="BG136" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH136" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>67</t>
         </is>
       </c>
       <c r="BI136" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ136" t="inlineStr"/>
@@ -38511,32 +38511,32 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>807726</t>
+          <t>676439</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>John Peck</t>
+          <t>Hunter Feduccia</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-09-20T18:10:00Z</t>
+          <t>2026-09-20T20:10:00Z</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Delayed Start</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -38546,17 +38546,17 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Davis Martin</t>
+          <t>Matt Wilkinson</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>663436</t>
+          <t>683363</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L137" t="n">
@@ -38574,17 +38574,17 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P137" t="n">
-        <v>34.4</v>
+        <v>27.1</v>
       </c>
       <c r="Q137" t="n">
-        <v>44.8</v>
+        <v>50.9</v>
       </c>
       <c r="R137" t="n">
-        <v>53.6</v>
+        <v>63.1</v>
       </c>
       <c r="S137" t="n">
         <v>44.8</v>
@@ -38593,7 +38593,7 @@
         <v>50</v>
       </c>
       <c r="U137" t="n">
-        <v>8.5</v>
+        <v>0.8</v>
       </c>
       <c r="V137" t="inlineStr">
         <is>
@@ -38628,7 +38628,7 @@
       <c r="AB137" t="inlineStr"/>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD137" t="inlineStr"/>
@@ -38645,12 +38645,12 @@
       </c>
       <c r="AH137" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ137" t="inlineStr">
@@ -38660,127 +38660,127 @@
       </c>
       <c r="AK137" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/17, 0 HR</t>
+          <t>Last 7 games: 2/16, 0 HR</t>
         </is>
       </c>
       <c r="AL137" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.4% barrel, 15.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.7% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN137" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AQ137" t="inlineStr">
         <is>
-          <t>98.866</t>
+          <t>98.7756</t>
         </is>
       </c>
       <c r="AR137" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>0.3475</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>0.1206</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>0.3058</t>
         </is>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>70.71</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>12.56</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>32.73</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>26.89</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>0.085</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>44.67</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>90.42</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="BD137" t="inlineStr">
         <is>
-          <t>0.4293</t>
+          <t>0.444</t>
         </is>
       </c>
       <c r="BE137" t="inlineStr">
         <is>
-          <t>0.1573</t>
+          <t>0.187</t>
         </is>
       </c>
       <c r="BF137" t="inlineStr">
         <is>
-          <t>23.97</t>
+          <t>32.3</t>
         </is>
       </c>
       <c r="BG137" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH137" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI137" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ137" t="inlineStr"/>
@@ -38840,7 +38840,7 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="M138" t="inlineStr">
         <is>
@@ -38873,7 +38873,7 @@
         <v>50</v>
       </c>
       <c r="U138" t="n">
-        <v>21.5</v>
+        <v>19.5</v>
       </c>
       <c r="V138" t="inlineStr">
         <is>
@@ -38930,7 +38930,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ138" t="inlineStr">
@@ -38940,7 +38940,7 @@
       </c>
       <c r="AK138" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/19, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL138" t="inlineStr">
@@ -42480,7 +42480,7 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>39.3</v>
+        <v>39.2</v>
       </c>
       <c r="M151" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>50</v>
       </c>
       <c r="U151" t="n">
-        <v>36</v>
+        <v>33.9</v>
       </c>
       <c r="V151" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ151" t="inlineStr">
@@ -42580,7 +42580,7 @@
       </c>
       <c r="AK151" t="inlineStr">
         <is>
-          <t>Contact streak: 9/25 over last 7 games</t>
+          <t>Contact streak: 9/26 over last 7 games</t>
         </is>
       </c>
       <c r="AL151" t="inlineStr">
@@ -43130,7 +43130,7 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ153" t="inlineStr">
@@ -43140,7 +43140,7 @@
       </c>
       <c r="AK153" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 0 HR</t>
+          <t>Last 7 games: 2/18, 0 HR</t>
         </is>
       </c>
       <c r="AL153" t="inlineStr">
@@ -55715,7 +55715,7 @@
         <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>40.1</v>
+        <v>39.1</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -55772,7 +55772,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -56802,7 +56802,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>57.3</v>
+        <v>57.2</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -56835,7 +56835,7 @@
         <v>50</v>
       </c>
       <c r="U21" t="n">
-        <v>22.9</v>
+        <v>21.1</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -56892,7 +56892,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -56902,7 +56902,7 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/22, 0 HR</t>
+          <t>Last 7 games: 6/23, 0 HR</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
